--- a/base_prov/ml/ml_abbott_2026-07-17.xlsx
+++ b/base_prov/ml/ml_abbott_2026-07-17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\como se me cante\retail-chatbot-main\eci_abbott-main\base_prov\ml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9961E57-22D3-4A2D-9F85-67ECF3311D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1C494A-1F25-45AF-911A-1CFE4C14704F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="153">
   <si>
     <t>fecha</t>
   </si>
@@ -492,6 +492,9 @@
   </si>
   <si>
     <t>Bren</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1474,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1521,7 +1524,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -1571,7 +1574,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -1621,7 +1624,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1671,7 +1674,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -1721,7 +1724,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -1771,7 +1774,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -1821,7 +1824,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -1871,7 +1874,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -1921,7 +1924,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -1971,7 +1974,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -2021,7 +2024,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -2071,7 +2074,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -2121,7 +2124,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -2171,7 +2174,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -2221,7 +2224,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -2271,7 +2274,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -2321,7 +2324,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -2371,7 +2374,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -2421,7 +2424,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -2471,7 +2474,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -2521,7 +2524,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -2571,7 +2574,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -2621,7 +2624,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -2671,7 +2674,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -2721,7 +2724,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -2771,7 +2774,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -2821,7 +2824,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -2871,7 +2874,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -2921,7 +2924,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -2971,7 +2974,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -3021,7 +3024,7 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -3071,7 +3074,7 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -3121,7 +3124,7 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -3171,7 +3174,7 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -3221,7 +3224,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -3271,7 +3274,7 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -3321,7 +3324,7 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -3371,7 +3374,7 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -3421,7 +3424,7 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -3471,7 +3474,7 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -3521,7 +3524,7 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -3571,7 +3574,7 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -3621,7 +3624,7 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -3671,7 +3674,7 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -3721,7 +3724,7 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -3771,7 +3774,7 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -3821,7 +3824,7 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -3871,7 +3874,7 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -3918,7 +3921,7 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -3965,7 +3968,7 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4012,7 +4015,7 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -4059,7 +4062,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -4106,7 +4109,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -4153,7 +4156,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -4200,7 +4203,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -4247,7 +4250,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -4294,7 +4297,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -4341,7 +4344,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -4388,7 +4391,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -4435,7 +4438,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -4482,7 +4485,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -4529,7 +4532,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -4576,7 +4579,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -4623,7 +4626,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -4670,7 +4673,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -4717,7 +4720,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -4764,7 +4767,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
